--- a/data/trans_orig/P29A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P29A-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2007</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2007 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242747</t>
+          <t>242797</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>286902</t>
+          <t>286717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151167</t>
+          <t>148004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192814</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>403913</t>
+          <t>406553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>465406</t>
+          <t>464851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202193</t>
+          <t>202378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246348</t>
+          <t>246298</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271695</t>
+          <t>276381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313342</t>
+          <t>316505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>488198</t>
+          <t>488753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>549691</t>
+          <t>547051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>443805</t>
+          <t>445132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>498873</t>
+          <t>498039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181902</t>
+          <t>182194</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>230660</t>
+          <t>229973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642961</t>
+          <t>639642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>716600</t>
+          <t>712969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>223618</t>
+          <t>224452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>278686</t>
+          <t>277359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393799</t>
+          <t>394486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442557</t>
+          <t>442265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>630349</t>
+          <t>633980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>703988</t>
+          <t>707307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>353935</t>
+          <t>351524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>405127</t>
+          <t>403189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183813</t>
+          <t>183631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>230144</t>
+          <t>232919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>541252</t>
+          <t>548551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>619811</t>
+          <t>623742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226370</t>
+          <t>228308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277562</t>
+          <t>279973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>452169</t>
+          <t>449394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>498500</t>
+          <t>498682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>693999</t>
+          <t>690068</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>772558</t>
+          <t>765259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>276543</t>
+          <t>275062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>320845</t>
+          <t>320640</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111737</t>
+          <t>108498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150249</t>
+          <t>148696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>395523</t>
+          <t>402709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>460006</t>
+          <t>465347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191467</t>
+          <t>191672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235769</t>
+          <t>237250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360054</t>
+          <t>361607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>398566</t>
+          <t>401805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>562609</t>
+          <t>557268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>627092</t>
+          <t>619906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149191</t>
+          <t>149802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189091</t>
+          <t>186954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54461</t>
+          <t>54655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85138</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214317</t>
+          <t>213806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266798</t>
+          <t>266253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191690</t>
+          <t>193827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>231590</t>
+          <t>230979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>317841</t>
+          <t>318151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348518</t>
+          <t>348324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>516962</t>
+          <t>517507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569443</t>
+          <t>569954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,72%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107387</t>
+          <t>107291</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>138970</t>
+          <t>139957</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38517</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130128</t>
+          <t>129431</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>173263</t>
+          <t>170693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149296</t>
+          <t>148309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180879</t>
+          <t>180975</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>304417</t>
+          <t>304381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>324051</t>
+          <t>324500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>457937</t>
+          <t>460507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501072</t>
+          <t>501769</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57275</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83771</t>
+          <t>84964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24617</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68590</t>
+          <t>69366</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104310</t>
+          <t>104489</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124391</t>
+          <t>123198</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150887</t>
+          <t>150860</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>308166</t>
+          <t>306899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>323991</t>
+          <t>324012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>436635</t>
+          <t>436456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>472355</t>
+          <t>471579</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1721081</t>
+          <t>1711533</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1830050</t>
+          <t>1832417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>774438</t>
+          <t>776264</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>871859</t>
+          <t>875351</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2521204</t>
+          <t>2521776</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2681089</t>
+          <t>2683702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1402553</t>
+          <t>1400186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1511522</t>
+          <t>1521070</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2488420</t>
+          <t>2484928</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2585841</t>
+          <t>2584015</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3911793</t>
+          <t>3909180</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4071678</t>
+          <t>4071106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2012</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2012 (tasa de respuesta: 96,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>235033</t>
+          <t>236615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>277515</t>
+          <t>278866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146297</t>
+          <t>146651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188160</t>
+          <t>188756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>393116</t>
+          <t>395226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>450784</t>
+          <t>454241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,42%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162754</t>
+          <t>161403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205236</t>
+          <t>203654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238102</t>
+          <t>237506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279965</t>
+          <t>279611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>415747</t>
+          <t>412290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473415</t>
+          <t>471305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>390230</t>
+          <t>391401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>439459</t>
+          <t>441090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>162271</t>
+          <t>163347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>207728</t>
+          <t>212523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>560803</t>
+          <t>559477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>632258</t>
+          <t>632956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>214257</t>
+          <t>212626</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263486</t>
+          <t>262315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389327</t>
+          <t>384532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>434784</t>
+          <t>433708</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>618514</t>
+          <t>617816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>689969</t>
+          <t>691295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>363079</t>
+          <t>364149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>413292</t>
+          <t>416371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>175700</t>
+          <t>176845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225371</t>
+          <t>227121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>552915</t>
+          <t>554459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>626072</t>
+          <t>627914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239223</t>
+          <t>236144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289436</t>
+          <t>288366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463808</t>
+          <t>462058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513479</t>
+          <t>512334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>715622</t>
+          <t>713780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>788779</t>
+          <t>787235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,67%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>329393</t>
+          <t>327543</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>377238</t>
+          <t>378234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163842</t>
+          <t>162939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211961</t>
+          <t>215163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>500942</t>
+          <t>506004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>579690</t>
+          <t>579985</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204065</t>
+          <t>203069</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>251910</t>
+          <t>253760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>389138</t>
+          <t>385936</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>437257</t>
+          <t>438160</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>602712</t>
+          <t>602417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>681460</t>
+          <t>676398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,21%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185894</t>
+          <t>182316</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>228188</t>
+          <t>226053</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76385</t>
+          <t>76841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113072</t>
+          <t>114558</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>271167</t>
+          <t>271952</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>327055</t>
+          <t>330153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180294</t>
+          <t>182429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>222588</t>
+          <t>226166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324216</t>
+          <t>322730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360903</t>
+          <t>360447</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>518715</t>
+          <t>515617</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>574603</t>
+          <t>573818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119910</t>
+          <t>119996</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>157468</t>
+          <t>154675</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57915</t>
+          <t>57373</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>154728</t>
+          <t>158079</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>206639</t>
+          <t>205927</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137309</t>
+          <t>140102</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174867</t>
+          <t>174781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>289461</t>
+          <t>290003</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315726</t>
+          <t>315541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435514</t>
+          <t>436226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>487425</t>
+          <t>484074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65501</t>
+          <t>63400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96544</t>
+          <t>95332</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81345</t>
+          <t>80352</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121101</t>
+          <t>121077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146970</t>
+          <t>148182</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178013</t>
+          <t>180114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>357150</t>
+          <t>357684</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>374941</t>
+          <t>375368</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>510294</t>
+          <t>510318</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>550050</t>
+          <t>551043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1779918</t>
+          <t>1778373</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1902363</t>
+          <t>1900727</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>846381</t>
+          <t>846842</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>953364</t>
+          <t>949519</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2656385</t>
+          <t>2647611</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2820098</t>
+          <t>2819507</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1372213</t>
+          <t>1373849</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1494658</t>
+          <t>1496203</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2532777</t>
+          <t>2536622</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2639760</t>
+          <t>2639299</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3940618</t>
+          <t>3941209</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4104331</t>
+          <t>4113105</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2016</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2016 (tasa de respuesta: 97,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>216121</t>
+          <t>218266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>257868</t>
+          <t>257647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>142814</t>
+          <t>143173</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179778</t>
+          <t>181353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>373618</t>
+          <t>371283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>429711</t>
+          <t>429425</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>147865</t>
+          <t>148086</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189612</t>
+          <t>187467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212206</t>
+          <t>210631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249170</t>
+          <t>248811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368006</t>
+          <t>368292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>424099</t>
+          <t>426434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>321318</t>
+          <t>321543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>369664</t>
+          <t>365761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195988</t>
+          <t>194024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>238812</t>
+          <t>239506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>527736</t>
+          <t>531325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>594322</t>
+          <t>597032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207829</t>
+          <t>211732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>256175</t>
+          <t>255950</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316870</t>
+          <t>316176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359694</t>
+          <t>361658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>538854</t>
+          <t>536144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>605440</t>
+          <t>601851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>382388</t>
+          <t>385402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>434015</t>
+          <t>435291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>208483</t>
+          <t>210455</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259334</t>
+          <t>256673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>612594</t>
+          <t>606712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>678189</t>
+          <t>677115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214798</t>
+          <t>213522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>266425</t>
+          <t>263411</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391251</t>
+          <t>393912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442102</t>
+          <t>440130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621210</t>
+          <t>622284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686805</t>
+          <t>692687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>345562</t>
+          <t>344847</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>396952</t>
+          <t>394613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>217470</t>
+          <t>218549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>268494</t>
+          <t>265779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>579003</t>
+          <t>577123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>651764</t>
+          <t>649002</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230649</t>
+          <t>232988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282039</t>
+          <t>282754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363694</t>
+          <t>366409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414718</t>
+          <t>413639</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>608025</t>
+          <t>610787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>680786</t>
+          <t>682666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,19%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>241767</t>
+          <t>241513</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>283827</t>
+          <t>284889</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101843</t>
+          <t>102320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143032</t>
+          <t>146139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>354714</t>
+          <t>356348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>416877</t>
+          <t>419356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171716</t>
+          <t>170654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213776</t>
+          <t>214030</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>343079</t>
+          <t>339972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>384268</t>
+          <t>383791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>524778</t>
+          <t>522299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>586941</t>
+          <t>585307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>146269</t>
+          <t>147103</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>182569</t>
+          <t>182258</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49622</t>
+          <t>50383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81182</t>
+          <t>80241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203640</t>
+          <t>203534</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>253871</t>
+          <t>253505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140003</t>
+          <t>140314</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176303</t>
+          <t>175469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>294856</t>
+          <t>295797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>326416</t>
+          <t>325655</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>444739</t>
+          <t>445105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>494970</t>
+          <t>495076</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75054</t>
+          <t>74561</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102933</t>
+          <t>103131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46239</t>
+          <t>44809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>98462</t>
+          <t>100257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139091</t>
+          <t>139581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146857</t>
+          <t>146659</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174736</t>
+          <t>175229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>349236</t>
+          <t>350666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>375679</t>
+          <t>375894</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>506174</t>
+          <t>505684</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>546803</t>
+          <t>545008</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,46%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1821769</t>
+          <t>1819409</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1933711</t>
+          <t>1934282</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1019800</t>
+          <t>1016079</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1131476</t>
+          <t>1129875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2868467</t>
+          <t>2873027</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3039082</t>
+          <t>3037583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1353835</t>
+          <t>1353264</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1465777</t>
+          <t>1468137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2356588</t>
+          <t>2358189</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2468264</t>
+          <t>2471985</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3736528</t>
+          <t>3738027</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3907143</t>
+          <t>3902583</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2023</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134189</t>
+          <t>136960</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202688</t>
+          <t>207277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78515</t>
+          <t>78120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123353</t>
+          <t>123409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231975</t>
+          <t>235074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>313811</t>
+          <t>314505</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197299</t>
+          <t>192710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265798</t>
+          <t>263027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189847</t>
+          <t>189791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234685</t>
+          <t>235080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>399376</t>
+          <t>398682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>481212</t>
+          <t>478113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203035</t>
+          <t>205863</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>254142</t>
+          <t>255629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89313</t>
+          <t>89548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172415</t>
+          <t>176236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281636</t>
+          <t>277314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>416113</t>
+          <t>422419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169405</t>
+          <t>167918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>220512</t>
+          <t>217684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338181</t>
+          <t>334360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>421283</t>
+          <t>421048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>518030</t>
+          <t>511724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>652507</t>
+          <t>656829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>258676</t>
+          <t>257528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>304363</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133826</t>
+          <t>133670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167718</t>
+          <t>167495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>403557</t>
+          <t>404064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>465544</t>
+          <t>465955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231811</t>
+          <t>231766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277498</t>
+          <t>278646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>373297</t>
+          <t>373520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>407189</t>
+          <t>407345</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611644</t>
+          <t>611233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673631</t>
+          <t>673124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157400</t>
+          <t>165470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>490811</t>
+          <t>485849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161989</t>
+          <t>158478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213746</t>
+          <t>213751</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>299719</t>
+          <t>318281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>647740</t>
+          <t>653228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>392688</t>
+          <t>397650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>726099</t>
+          <t>718029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>498310</t>
+          <t>498305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>550067</t>
+          <t>553578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>947816</t>
+          <t>942328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1295837</t>
+          <t>1277275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,05%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>240780</t>
+          <t>243187</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>285212</t>
+          <t>287823</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119299</t>
+          <t>119573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148430</t>
+          <t>149822</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371879</t>
+          <t>371793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>431401</t>
+          <t>426652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274992</t>
+          <t>272381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>319424</t>
+          <t>317017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>395415</t>
+          <t>394023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424546</t>
+          <t>424272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>672648</t>
+          <t>677397</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>732170</t>
+          <t>732256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>173341</t>
+          <t>174710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>206868</t>
+          <t>206538</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107776</t>
+          <t>108830</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>471068</t>
+          <t>478548</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>329138</t>
+          <t>328466</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>743419</t>
+          <t>721912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160421</t>
+          <t>160751</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193948</t>
+          <t>192579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136704</t>
+          <t>129224</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>499996</t>
+          <t>498942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>231642</t>
+          <t>253149</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>645923</t>
+          <t>646595</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86553</t>
+          <t>87432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112119</t>
+          <t>112884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35613</t>
+          <t>35429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112035</t>
+          <t>111488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>144612</t>
+          <t>143231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170229</t>
+          <t>169464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>195795</t>
+          <t>194916</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>388250</t>
+          <t>388434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>402787</t>
+          <t>402823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>561599</t>
+          <t>562980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>594176</t>
+          <t>594723</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1248887</t>
+          <t>1200308</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1719386</t>
+          <t>1723251</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>851493</t>
+          <t>850746</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1468125</t>
+          <t>1518369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2375497</t>
+          <t>2351846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3032422</t>
+          <t>3000156</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1733662</t>
+          <t>1729797</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2204161</t>
+          <t>2252740</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2184221</t>
+          <t>2133977</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2800853</t>
+          <t>2801600</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4072973</t>
+          <t>4105239</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4729898</t>
+          <t>4753549</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P29A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P29A-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242797</t>
+          <t>241690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>286717</t>
+          <t>284971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148004</t>
+          <t>149022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188128</t>
+          <t>191575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>406553</t>
+          <t>404730</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>464851</t>
+          <t>465581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202378</t>
+          <t>204124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246298</t>
+          <t>247405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276381</t>
+          <t>272934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>316505</t>
+          <t>315487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>488753</t>
+          <t>488023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>547051</t>
+          <t>548874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>445132</t>
+          <t>446338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>498039</t>
+          <t>498877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>182194</t>
+          <t>182347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>231459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>639642</t>
+          <t>639097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>712969</t>
+          <t>714884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224452</t>
+          <t>223614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>277359</t>
+          <t>276153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394486</t>
+          <t>393000</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442265</t>
+          <t>442112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>633980</t>
+          <t>632065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707307</t>
+          <t>707852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>351524</t>
+          <t>351213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>403189</t>
+          <t>401781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183631</t>
+          <t>183979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>232919</t>
+          <t>231215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>548551</t>
+          <t>545851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>623742</t>
+          <t>622219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228308</t>
+          <t>229716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279973</t>
+          <t>280284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449394</t>
+          <t>451098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>498682</t>
+          <t>498334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>690068</t>
+          <t>691591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>765259</t>
+          <t>767959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>275062</t>
+          <t>277940</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>320640</t>
+          <t>322873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108498</t>
+          <t>111179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148696</t>
+          <t>150527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>402709</t>
+          <t>397975</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>465347</t>
+          <t>460589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,04%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191672</t>
+          <t>189439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237250</t>
+          <t>234372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361607</t>
+          <t>359776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>401805</t>
+          <t>399124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>557268</t>
+          <t>562026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>619906</t>
+          <t>624640</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,08%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149802</t>
+          <t>150337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>186954</t>
+          <t>189175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54655</t>
+          <t>54963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84828</t>
+          <t>85394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213806</t>
+          <t>214994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266253</t>
+          <t>261516</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193827</t>
+          <t>191606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230979</t>
+          <t>230444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>318151</t>
+          <t>317585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348324</t>
+          <t>348016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>517507</t>
+          <t>522244</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569954</t>
+          <t>568766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107291</t>
+          <t>105442</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>139957</t>
+          <t>138353</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129431</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>170693</t>
+          <t>171727</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148309</t>
+          <t>149913</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180975</t>
+          <t>182824</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>304381</t>
+          <t>304986</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>324500</t>
+          <t>324330</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>460507</t>
+          <t>459473</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501769</t>
+          <t>502260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>55911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84964</t>
+          <t>82929</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69366</t>
+          <t>69685</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104489</t>
+          <t>102136</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123198</t>
+          <t>125233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150860</t>
+          <t>152251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>306899</t>
+          <t>307406</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>324012</t>
+          <t>324341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>436456</t>
+          <t>438809</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>471579</t>
+          <t>471260</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1711533</t>
+          <t>1720474</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1832417</t>
+          <t>1832180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>776264</t>
+          <t>771836</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>875351</t>
+          <t>872284</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2521776</t>
+          <t>2512024</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2683702</t>
+          <t>2675544</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1400186</t>
+          <t>1400423</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1521070</t>
+          <t>1512129</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2484928</t>
+          <t>2487995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2584015</t>
+          <t>2588443</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3909180</t>
+          <t>3917338</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4071106</t>
+          <t>4080858</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>236615</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>278866</t>
+          <t>276208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>146651</t>
+          <t>146305</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188756</t>
+          <t>186702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>395226</t>
+          <t>392435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>454241</t>
+          <t>451903</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,15%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161403</t>
+          <t>164061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203654</t>
+          <t>205328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237506</t>
+          <t>239560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279611</t>
+          <t>279957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>412290</t>
+          <t>414628</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>471305</t>
+          <t>474096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>391401</t>
+          <t>391033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>441090</t>
+          <t>440631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163347</t>
+          <t>161245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212523</t>
+          <t>205758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>559477</t>
+          <t>562519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>632956</t>
+          <t>632662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212626</t>
+          <t>213085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262315</t>
+          <t>262683</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>384532</t>
+          <t>391297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>433708</t>
+          <t>435810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617816</t>
+          <t>618110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>691295</t>
+          <t>688253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>364149</t>
+          <t>364177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>416371</t>
+          <t>416884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176845</t>
+          <t>175213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>227121</t>
+          <t>225697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>554459</t>
+          <t>551175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627914</t>
+          <t>627718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>236144</t>
+          <t>235631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288366</t>
+          <t>288338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>462058</t>
+          <t>463482</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>512334</t>
+          <t>513966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>713780</t>
+          <t>713976</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>787235</t>
+          <t>790519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>327543</t>
+          <t>328211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>378234</t>
+          <t>379399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162939</t>
+          <t>161832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215163</t>
+          <t>210915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>506004</t>
+          <t>503090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>579985</t>
+          <t>576931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,79%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>203069</t>
+          <t>201904</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>253760</t>
+          <t>253092</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385936</t>
+          <t>390184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>438160</t>
+          <t>439267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>602417</t>
+          <t>605471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>676398</t>
+          <t>679312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182316</t>
+          <t>183296</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>226053</t>
+          <t>224968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76841</t>
+          <t>78142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114558</t>
+          <t>114849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>271952</t>
+          <t>273367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>330153</t>
+          <t>329154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182429</t>
+          <t>183514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>226166</t>
+          <t>225186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>322730</t>
+          <t>322439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360447</t>
+          <t>359146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>515617</t>
+          <t>516616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>573818</t>
+          <t>572403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119996</t>
+          <t>119942</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154675</t>
+          <t>156410</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57373</t>
+          <t>57403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158079</t>
+          <t>158582</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205927</t>
+          <t>206525</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140102</t>
+          <t>138367</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174781</t>
+          <t>174835</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290003</t>
+          <t>289973</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315541</t>
+          <t>316418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436226</t>
+          <t>435628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>484074</t>
+          <t>483571</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63400</t>
+          <t>63196</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95332</t>
+          <t>95025</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80352</t>
+          <t>81023</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121077</t>
+          <t>122405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>148182</t>
+          <t>148489</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>180114</t>
+          <t>180318</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>357684</t>
+          <t>357446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>375368</t>
+          <t>376075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>510318</t>
+          <t>508990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>551043</t>
+          <t>550372</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1778373</t>
+          <t>1775043</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1900727</t>
+          <t>1894175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>846842</t>
+          <t>846100</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>949519</t>
+          <t>953775</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2647611</t>
+          <t>2645986</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2819507</t>
+          <t>2819861</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1373849</t>
+          <t>1380401</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1496203</t>
+          <t>1499533</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2536622</t>
+          <t>2532366</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2639299</t>
+          <t>2640041</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3941209</t>
+          <t>3940855</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4113105</t>
+          <t>4114730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>218266</t>
+          <t>216190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>257647</t>
+          <t>259079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143173</t>
+          <t>142636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181353</t>
+          <t>180556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>371283</t>
+          <t>371632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>429425</t>
+          <t>426347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148086</t>
+          <t>146654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187467</t>
+          <t>189543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210631</t>
+          <t>211428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248811</t>
+          <t>249348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368292</t>
+          <t>371370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>426434</t>
+          <t>426085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>321543</t>
+          <t>320330</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>365761</t>
+          <t>367949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194024</t>
+          <t>195793</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239506</t>
+          <t>241348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>531325</t>
+          <t>531272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>597032</t>
+          <t>597615</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211732</t>
+          <t>209544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>255950</t>
+          <t>257163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316176</t>
+          <t>314334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361658</t>
+          <t>359889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>536144</t>
+          <t>535561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601851</t>
+          <t>601904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>385402</t>
+          <t>384407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>435291</t>
+          <t>432780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210455</t>
+          <t>208663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256673</t>
+          <t>259688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>606712</t>
+          <t>606486</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>677115</t>
+          <t>678189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,19%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213522</t>
+          <t>216033</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263411</t>
+          <t>264406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>393912</t>
+          <t>390897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>440130</t>
+          <t>441922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622284</t>
+          <t>621210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692687</t>
+          <t>692913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>344847</t>
+          <t>344225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>394613</t>
+          <t>394381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218549</t>
+          <t>219275</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>265779</t>
+          <t>267281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>577123</t>
+          <t>575758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>649002</t>
+          <t>647813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>232988</t>
+          <t>233220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282754</t>
+          <t>283376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366409</t>
+          <t>364907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>413639</t>
+          <t>412913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>610787</t>
+          <t>611976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>682666</t>
+          <t>684031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>241513</t>
+          <t>238880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>284889</t>
+          <t>285391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102320</t>
+          <t>102001</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146139</t>
+          <t>143060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>356348</t>
+          <t>355156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>419356</t>
+          <t>419877</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170654</t>
+          <t>170152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214030</t>
+          <t>216663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339972</t>
+          <t>343051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>383791</t>
+          <t>384110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>522299</t>
+          <t>521778</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>585307</t>
+          <t>586499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>147103</t>
+          <t>147000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>182258</t>
+          <t>182596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50383</t>
+          <t>50806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80241</t>
+          <t>81445</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203534</t>
+          <t>204315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>253505</t>
+          <t>254185</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140314</t>
+          <t>139976</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175469</t>
+          <t>175572</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>295797</t>
+          <t>294593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325655</t>
+          <t>325232</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>445105</t>
+          <t>444425</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495076</t>
+          <t>494295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74561</t>
+          <t>73883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103131</t>
+          <t>102466</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19581</t>
+          <t>19826</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44809</t>
+          <t>45752</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>100257</t>
+          <t>100155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139581</t>
+          <t>141816</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146659</t>
+          <t>147324</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175229</t>
+          <t>175907</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>350666</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>375894</t>
+          <t>375649</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>505684</t>
+          <t>503449</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>545008</t>
+          <t>545110</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1819409</t>
+          <t>1819001</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1934282</t>
+          <t>1933753</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1016079</t>
+          <t>1017218</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1129875</t>
+          <t>1127265</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2873027</t>
+          <t>2865621</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3037583</t>
+          <t>3032254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1353264</t>
+          <t>1353793</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1468137</t>
+          <t>1468545</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2358189</t>
+          <t>2360799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2471985</t>
+          <t>2470846</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3738027</t>
+          <t>3743356</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3902583</t>
+          <t>3909989</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,71%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>169903</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136960</t>
+          <t>138477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>207277</t>
+          <t>200980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78120</t>
+          <t>88356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123409</t>
+          <t>137311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>270753</t>
+          <t>279083</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235074</t>
+          <t>238513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>314505</t>
+          <t>315502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>230084</t>
+          <t>241550</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>192710</t>
+          <t>206813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263027</t>
+          <t>269316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>212349</t>
+          <t>249671</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189791</t>
+          <t>225201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235080</t>
+          <t>274156</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>442434</t>
+          <t>491222</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>398682</t>
+          <t>454803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>478113</t>
+          <t>531792</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>230135</t>
+          <t>249464</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205863</t>
+          <t>219816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>255629</t>
+          <t>277212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>142253</t>
+          <t>152991</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89548</t>
+          <t>132346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176236</t>
+          <t>174853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>372388</t>
+          <t>402455</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>277314</t>
+          <t>364411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>422419</t>
+          <t>435316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>193412</t>
+          <t>227426</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>167918</t>
+          <t>199678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217684</t>
+          <t>257074</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>368343</t>
+          <t>347112</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>334360</t>
+          <t>325250</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>421048</t>
+          <t>367757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>561755</t>
+          <t>574539</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>511724</t>
+          <t>541678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656829</t>
+          <t>612583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>62,7%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510596</t>
+          <t>500103</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510596</t>
+          <t>500103</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510596</t>
+          <t>500103</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934143</t>
+          <t>976994</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934143</t>
+          <t>976994</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934143</t>
+          <t>976994</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>282184</t>
+          <t>312784</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>257528</t>
+          <t>286794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>340212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>150814</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133670</t>
+          <t>150613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167495</t>
+          <t>190108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>432997</t>
+          <t>482720</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>404064</t>
+          <t>448986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>465955</t>
+          <t>516468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>41,64%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>253990</t>
+          <t>306875</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231766</t>
+          <t>279447</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278646</t>
+          <t>332865</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>390201</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>373520</t>
+          <t>430406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>407345</t>
+          <t>469901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>644191</t>
+          <t>757453</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611233</t>
+          <t>723705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673124</t>
+          <t>791187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541015</t>
+          <t>620514</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541015</t>
+          <t>620514</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541015</t>
+          <t>620514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077188</t>
+          <t>1240173</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077188</t>
+          <t>1240173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077188</t>
+          <t>1240173</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>344267</t>
+          <t>354936</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165470</t>
+          <t>327875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>485849</t>
+          <t>379244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>192392</t>
+          <t>212010</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158478</t>
+          <t>193619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213751</t>
+          <t>230720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>536659</t>
+          <t>566946</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>318281</t>
+          <t>532300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>653228</t>
+          <t>602544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>539232</t>
+          <t>341314</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>397650</t>
+          <t>317006</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>718029</t>
+          <t>368375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>519664</t>
+          <t>523480</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>498305</t>
+          <t>504770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>553578</t>
+          <t>541871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1058897</t>
+          <t>864794</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>942328</t>
+          <t>829196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1277275</t>
+          <t>899440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>62,82%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>883499</t>
+          <t>696250</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>883499</t>
+          <t>696250</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>883499</t>
+          <t>696250</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712056</t>
+          <t>735490</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712056</t>
+          <t>735490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712056</t>
+          <t>735490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1595556</t>
+          <t>1431740</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1595556</t>
+          <t>1431740</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1595556</t>
+          <t>1431740</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>264194</t>
+          <t>281793</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>243187</t>
+          <t>260643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>287823</t>
+          <t>304235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>134297</t>
+          <t>147527</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119573</t>
+          <t>129568</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149822</t>
+          <t>162661</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>398490</t>
+          <t>429319</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371793</t>
+          <t>397545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>426652</t>
+          <t>458806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>296010</t>
+          <t>326472</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>272381</t>
+          <t>304030</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>317017</t>
+          <t>347622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>409548</t>
+          <t>458809</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>394023</t>
+          <t>443675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424272</t>
+          <t>476768</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>705559</t>
+          <t>785282</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>677397</t>
+          <t>755795</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>732256</t>
+          <t>817056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>543845</t>
+          <t>606336</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>543845</t>
+          <t>606336</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>543845</t>
+          <t>606336</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104049</t>
+          <t>1214601</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104049</t>
+          <t>1214601</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104049</t>
+          <t>1214601</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>189996</t>
+          <t>207876</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>174710</t>
+          <t>191928</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>206538</t>
+          <t>224612</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>280153</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>108830</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>478548</t>
+          <t>92312</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>470149</t>
+          <t>288688</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>328466</t>
+          <t>267953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>721912</t>
+          <t>312162</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>177293</t>
+          <t>198278</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160751</t>
+          <t>181542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192579</t>
+          <t>214226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>327619</t>
+          <t>357675</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>129224</t>
+          <t>346175</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>498942</t>
+          <t>368426</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>504912</t>
+          <t>555953</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253149</t>
+          <t>532479</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>646595</t>
+          <t>576688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367289</t>
+          <t>406154</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367289</t>
+          <t>406154</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367289</t>
+          <t>406154</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607772</t>
+          <t>438487</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607772</t>
+          <t>438487</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607772</t>
+          <t>438487</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975061</t>
+          <t>844641</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975061</t>
+          <t>844641</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975061</t>
+          <t>844641</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>99624</t>
+          <t>109317</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87432</t>
+          <t>94797</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112884</t>
+          <t>124420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>31533</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>23783</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35429</t>
+          <t>41313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>127058</t>
+          <t>140850</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111488</t>
+          <t>123733</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143231</t>
+          <t>157587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>182724</t>
+          <t>200457</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169464</t>
+          <t>185354</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194916</t>
+          <t>214977</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>396430</t>
+          <t>430778</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>388434</t>
+          <t>420998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>402823</t>
+          <t>438528</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>579153</t>
+          <t>631235</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>562980</t>
+          <t>614498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>594723</t>
+          <t>648352</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,97%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282348</t>
+          <t>309774</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282348</t>
+          <t>309774</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282348</t>
+          <t>309774</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423863</t>
+          <t>462311</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>423863</t>
+          <t>462311</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>423863</t>
+          <t>462311</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706211</t>
+          <t>772085</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706211</t>
+          <t>772085</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706211</t>
+          <t>772085</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1580302</t>
+          <t>1682411</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1200308</t>
+          <t>1614562</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1723251</t>
+          <t>1751951</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1028192</t>
+          <t>907649</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>850746</t>
+          <t>859504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1518369</t>
+          <t>958057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2608494</t>
+          <t>2590061</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2351846</t>
+          <t>2494475</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3000156</t>
+          <t>2670491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1872746</t>
+          <t>1842374</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1729797</t>
+          <t>1772834</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2252740</t>
+          <t>1910223</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2624154</t>
+          <t>2818105</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2133977</t>
+          <t>2767697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2801600</t>
+          <t>2866250</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4496901</t>
+          <t>4660478</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4105239</t>
+          <t>4580048</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4753549</t>
+          <t>4756064</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3453048</t>
+          <t>3524785</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3453048</t>
+          <t>3524785</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3453048</t>
+          <t>3524785</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3652346</t>
+          <t>3725754</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3652346</t>
+          <t>3725754</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3652346</t>
+          <t>3725754</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7105395</t>
+          <t>7250539</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7105395</t>
+          <t>7250539</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7105395</t>
+          <t>7250539</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
